--- a/output/pdf_financials_xlsx/RMD.xlsx
+++ b/output/pdf_financials_xlsx/RMD.xlsx
@@ -1051,31 +1051,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.368823</v>
+        <v>-0.368823</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.390241</v>
+        <v>-0.390241</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.520292</v>
+        <v>-0.520292</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.289838</v>
+        <v>-0.289838</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.222132</v>
+        <v>-0.222648</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.279595</v>
+        <v>-0.279595</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.731565</v>
+        <v>-0.731565</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.373975</v>
+        <v>-0.373975</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.191427</v>
+        <v>-0.191427</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.15915</v>
@@ -1271,31 +1271,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.368823</v>
+        <v>-0.368823</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.390241</v>
+        <v>-0.390241</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.520292</v>
+        <v>-0.520292</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.289838</v>
+        <v>-0.289838</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.22239</v>
+        <v>-0.22239</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.279595</v>
+        <v>-0.279595</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.731565</v>
+        <v>-0.731565</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.373975</v>
+        <v>-0.373975</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.191427</v>
+        <v>-0.191427</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.15915</v>
@@ -1400,31 +1400,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.368823</v>
+        <v>-0.368823</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.390241</v>
+        <v>-0.390241</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.520292</v>
+        <v>-0.520292</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.289838</v>
+        <v>-0.289838</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.22239</v>
+        <v>-0.22239</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.279595</v>
+        <v>-0.279595</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.731565</v>
+        <v>-0.731565</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.373975</v>
+        <v>-0.373975</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.191427</v>
+        <v>-0.191427</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.15915</v>
@@ -1610,31 +1610,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.368823</v>
+        <v>-0.368823</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.390241</v>
+        <v>-0.390241</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.520292</v>
+        <v>-0.520292</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.289838</v>
+        <v>-0.289838</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.222132</v>
+        <v>-0.222648</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.279595</v>
+        <v>-0.279595</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.731565</v>
+        <v>-0.731565</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.373975</v>
+        <v>-0.373975</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.191427</v>
+        <v>-0.191427</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.15915</v>
@@ -1696,31 +1696,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.368823</v>
+        <v>-0.368823</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.390241</v>
+        <v>-0.390241</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.520292</v>
+        <v>-0.520292</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.289838</v>
+        <v>-0.289838</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.222132</v>
+        <v>-0.222648</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.281344</v>
+        <v>-0.277846</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.73327</v>
+        <v>-0.72986</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.375325</v>
+        <v>-0.372625</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.191916</v>
+        <v>-0.190938</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.158752</v>
@@ -1806,31 +1806,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.1161471557452326</v>
+        <v>-0.1158779777945456</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -20568,34 +20568,34 @@
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>0.368823</v>
+        <v>-0.368823</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>0.390241</v>
+        <v>-0.390241</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.520292</v>
+        <v>-0.520292</v>
       </c>
       <c r="H189" s="5" t="n">
-        <v>0.289838</v>
+        <v>-0.289838</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>0.22239</v>
+        <v>-0.22239</v>
       </c>
       <c r="J189" s="5" t="n">
-        <v>0.279595</v>
+        <v>-0.279595</v>
       </c>
       <c r="K189" s="5" t="n">
-        <v>0.731565</v>
+        <v>-0.731565</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>0.373975</v>
+        <v>-0.373975</v>
       </c>
       <c r="M189" s="5" t="n">
-        <v>0.191427</v>
+        <v>-0.191427</v>
       </c>
       <c r="N189" s="5" t="n">
-        <v>0.15915</v>
+        <v>-0.15915</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RMD.xlsx
+++ b/output/pdf_financials_xlsx/RMD.xlsx
@@ -909,10 +909,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000862</v>
       </c>
     </row>
     <row r="13">
@@ -1640,10 +1640,10 @@
         <v>-0.15915</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.760036</v>
+        <v>-0.7600440000000001</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.154991</v>
+        <v>-0.155853</v>
       </c>
     </row>
     <row r="28">
@@ -1726,10 +1726,10 @@
         <v>-0.158752</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.7597120000000001</v>
+        <v>-0.75972</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.154727</v>
+        <v>-0.155589</v>
       </c>
     </row>
     <row r="30">
@@ -1952,13 +1952,13 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.013793</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.389494</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005502</v>
       </c>
     </row>
     <row r="35">
@@ -2038,13 +2038,13 @@
         <v>0.000916</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.000398</v>
+        <v>0.014191</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.389494</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005502</v>
       </c>
     </row>
     <row r="37">
@@ -2578,13 +2578,13 @@
         <v>0.112626</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.020613</v>
+        <v>0.00682</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.539752</v>
+        <v>0.150258</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.098098</v>
+        <v>0.092596</v>
       </c>
     </row>
     <row r="49">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
